--- a/data/fichier_compl_toolbox.xlsx
+++ b/data/fichier_compl_toolbox.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vince\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vince\Desktop\GitHub\IT_CM_Toolbox_Website\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AB507E3-2271-4A35-9D9E-6CC8E4B71B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2C2F2E-D3F0-4C7E-97CF-64DD43FBABD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CFE606A8-A71B-4F16-BD7A-880BC1F5037A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
   <si>
     <t>Description</t>
   </si>
@@ -47,14 +47,6 @@
     <t>Cycle de communication</t>
   </si>
   <si>
-    <t>On met au courant sur les changements prévus. On vérifie que ces changements soient
-compris comme on l’entend et si ceux-ci provoquent des réactions positives ou non.
-On entame une discussion pour d’une part, négocier et d’autre part, intégrer des
-idées quant aux attentes divergentes des parties prenantes (aux réactions provoquées
-à l’étape 2). On synthétise le changement comme nouvellement planifié et on revient
-à l’étape 1.</t>
-  </si>
-  <si>
     <t>Entretiens</t>
   </si>
   <si>
@@ -79,14 +71,68 @@
     <t>Etiquettes</t>
   </si>
   <si>
-    <t>définition projet, exigences</t>
+    <t>définition projet, exigences,communication</t>
+  </si>
+  <si>
+    <t>Celui-ci consiste à informer sur le changement, vérifier la compréhension de ces informations, susciter des réactions et finalement nourrir la discussion afin d'améliorer ce projet de changement. Le cycle peut recommencer après ces améliorations.</t>
+  </si>
+  <si>
+    <t>transférer</t>
+  </si>
+  <si>
+    <t>Espace de travail flexible pour organiser vos tâches, vos projets et vos échéances en un seul endroit, à l'aide de bases de données pouvant être consultées sous plusieurs formes (listes, tableaux, calendriers). Permet la gestion de l'avancement des ajouts, modifications et complétions des tâches dans un espace centralisé.</t>
+  </si>
+  <si>
+    <t>modèle, communication</t>
+  </si>
+  <si>
+    <t>Modèle basé sur des questions pour pouvoir déterminer (grace à un proxi) quel type de raisonnement a une personne. Permet l'adaptation d'un discours pour convenir mieux à l'interlocuteur, ne pas choquer ou bloquer court aux discussions.</t>
+  </si>
+  <si>
+    <t>Tracker de tâches. (Ex : Notion ou Jira)</t>
+  </si>
+  <si>
+    <t>Modèle de catégorisation de pensée (Ex : DISC ou HBDI)</t>
+  </si>
+  <si>
+    <t>Préparation aux risques via IA conversationelle et configuration "Grill-Me" (Ex : Chatgpt, Claude, etc)</t>
+  </si>
+  <si>
+    <t>Discussion avec un agent conversationnel pour se challenger et se préparer à d'éventuels problèmes qui pourraient remonter (du terrain ou management). Important de fixer une limite car par principe la solution ne sera jamais parfaite.</t>
+  </si>
+  <si>
+    <t>IA, définition projet, comprendre</t>
+  </si>
+  <si>
+    <t>Plateforme de messagerie dédiée à la communication et à la collaboration au sein d'une équipe. Utilise des canaux, messages privés et intégrations pour organiser les conversations par thème ou par projet. Permet la gestion du flux de partage, de discussion et de suivi des tâches grâce à un espace centralisé et consultable.</t>
+  </si>
+  <si>
+    <t>application, communication</t>
+  </si>
+  <si>
+    <t>Plateforme de messagerie collaborative. (Ex : Teams ou Slack)</t>
+  </si>
+  <si>
+    <t>Listing des conditions qui permettront la réussite du projet, objectifs finaux et intermédiares permettant la bonne réussite du projet.</t>
+  </si>
+  <si>
+    <t>définition projet, objectifs, exigences</t>
+  </si>
+  <si>
+    <t>comprendre, objectifs, exigences, communication</t>
+  </si>
+  <si>
+    <t>Fini</t>
+  </si>
+  <si>
+    <t>Non</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -131,22 +177,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -181,12 +236,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{10F2806C-E9F6-4F68-B183-9F12382969E9}" name="Table1" displayName="Table1" ref="A1:C14" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="A1:C14" xr:uid="{10F2806C-E9F6-4F68-B183-9F12382969E9}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{2754BDFE-CC60-443C-9BAA-18CEABC07D01}" name="Outil" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{087C9761-2A1E-4247-AE26-DA46524F57CD}" name="Description" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{8B13619F-7B8E-4066-8EC4-55C4833E31BB}" name="Etiquettes" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{10F2806C-E9F6-4F68-B183-9F12382969E9}" name="Table1" displayName="Table1" ref="A1:D11" totalsRowShown="0" headerRowDxfId="5" dataDxfId="1">
+  <autoFilter ref="A1:D11" xr:uid="{10F2806C-E9F6-4F68-B183-9F12382969E9}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{2754BDFE-CC60-443C-9BAA-18CEABC07D01}" name="Outil" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{087C9761-2A1E-4247-AE26-DA46524F57CD}" name="Description" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{8B13619F-7B8E-4066-8EC4-55C4833E31BB}" name="Etiquettes" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{BACFC472-94B6-4AFD-B1F1-B1F90C606004}" name="Fini" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -509,114 +565,173 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F60179D4-D606-45E2-9272-BC7F4BB8B9F2}">
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.59765625" customWidth="1"/>
-    <col min="2" max="2" width="82.59765625" customWidth="1"/>
-    <col min="3" max="3" width="13.3984375" customWidth="1"/>
+    <col min="1" max="1" width="17.5546875" customWidth="1"/>
+    <col min="2" max="2" width="82.5546875" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" s="3" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="114" customHeight="1">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="D3" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="41.4">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="69">
-      <c r="A4" s="2" t="s">
+      <c r="D4" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2" t="s">
+      <c r="B5" s="4"/>
+      <c r="C5" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="55.2">
-      <c r="A5" s="2" t="s">
+      <c r="D5" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2" t="s">
+      <c r="B6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="55.2">
-      <c r="A6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="27.6">
-      <c r="A7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D7" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>

--- a/data/fichier_compl_toolbox.xlsx
+++ b/data/fichier_compl_toolbox.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vince\Desktop\GitHub\IT_CM_Toolbox_Website\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2C2F2E-D3F0-4C7E-97CF-64DD43FBABD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F75A5F-2ABB-4564-9F7C-4262742C2095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CFE606A8-A71B-4F16-BD7A-880BC1F5037A}"/>
   </bookViews>
@@ -36,14 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="69">
   <si>
     <t>Description</t>
   </si>
   <si>
-    <t>définition projet</t>
-  </si>
-  <si>
     <t>Cycle de communication</t>
   </si>
   <si>
@@ -116,6 +113,9 @@
     <t>Listing des conditions qui permettront la réussite du projet, objectifs finaux et intermédiares permettant la bonne réussite du projet.</t>
   </si>
   <si>
+    <t>définition projet, objectifs</t>
+  </si>
+  <si>
     <t>définition projet, objectifs, exigences</t>
   </si>
   <si>
@@ -126,6 +126,123 @@
   </si>
   <si>
     <t>Non</t>
+  </si>
+  <si>
+    <t>Manière de rencontrer et récolter de l'information sur un projet en mettant l'emphase sur la rencontre individuelle d'intervenants-clés et des questions spécifiques. Permet d'avoir des réponses précises sur des questions choisies au préalable.</t>
+  </si>
+  <si>
+    <t>définition projet, equipe</t>
+  </si>
+  <si>
+    <t>Liste de questions pour aider à définir un projet de changement. Des questions sur la direction du projet, le pourquoi, la question du timing, les bénéfices et finalement comment s'y prendre.</t>
+  </si>
+  <si>
+    <t>Former une équipe spécifiquement pour s'occuper du changement permet d'avoir des gens dévoués et qui s'occuperont à fond de créer un climat opportun à la mise en place du projet de changement. A utiliser particulièrement dans des projets d'envergure et/ou avec un impact significatif. Idéalement, au moins un gestionnaire du changement (formé ou au moins ayant cette sensibilité) devrait faire partie de l'équipe.</t>
+  </si>
+  <si>
+    <t>définition projet, objectifs, communication</t>
+  </si>
+  <si>
+    <t>BPMN</t>
+  </si>
+  <si>
+    <t>Diagramme d'activités</t>
+  </si>
+  <si>
+    <t>Archimate</t>
+  </si>
+  <si>
+    <t>Wiki du projet (Ex : Confluence)</t>
+  </si>
+  <si>
+    <t>Plateforme de documentation (Ex : Sharepoint)</t>
+  </si>
+  <si>
+    <t>Notation servant à représenter les processus / flows business. Permet une communication et documentation plus claire des processus métiers. Cette notation permet d'envisager des changements et améliorations aux processus métiers. Langage assez riche et contraignant.</t>
+  </si>
+  <si>
+    <t>Modélisation servant à représenter des processus métiers. Notation plus simple d'utilisation mais plus limitante (en terme de possibilités d'amélioration) que BPMN.</t>
+  </si>
+  <si>
+    <t>Système architectural de modélisation permettant une analyse détaillée par couche. Les 3 couches étant le business (globalement les flows / processus métiers), la couche à propos des nécessités des applications et finalement la couche des technologies physiques. Ce langage de modélisation est complexe mais permet une vue d'ensemble de l'architecture IT (matérielle et immatérielle) autour d'un processus.</t>
+  </si>
+  <si>
+    <t>Utiliser un wiki pour documenter les parties d'un projet est une manière de documenter en détail les aspects d'un projet. Chaque partie du projet peut être ajoutée et c'est particulièrement intéressant pour documenter les détails peu commun / d'intérêt ou sur lequel on pourrait se méprendre.</t>
+  </si>
+  <si>
+    <t>modélisation, communication, comprendre, définition projet, analyse</t>
+  </si>
+  <si>
+    <t>transfert, documentation, comprendre</t>
+  </si>
+  <si>
+    <t>Réseau de pages pouvant servir à documenter, ouvrir certaines applications et d'autres utilités directement dans une et même plateforme. Peut servir d'intranet.</t>
+  </si>
+  <si>
+    <t>documentation, réseau</t>
+  </si>
+  <si>
+    <t>modélisation, communication, comprendre, définition projet, analyse, exigences</t>
+  </si>
+  <si>
+    <t>Utiliser un registre des risques</t>
+  </si>
+  <si>
+    <t>Sert à lister les risques et à suivre leur évolution au fur et à mesure d'un changement. En change management, on parle ici surtout de risques humains et liés à l'organisation. Ces risques peuvent être mesurés et comparés à l'aide d'une matrice.</t>
+  </si>
+  <si>
+    <t>risques, objectifs, adhérer, analyse</t>
+  </si>
+  <si>
+    <t>Ateliers de coconstruction</t>
+  </si>
+  <si>
+    <t>Processus axés clients / utilisateurs. L'idée est de faire des groupes avec des key-users différents pour légitimer le projet de changement ainsi que bénéficier de l'intelligence collective.</t>
+  </si>
+  <si>
+    <t>communication, adhérer</t>
+  </si>
+  <si>
+    <t>Discours d'ascenseur</t>
+  </si>
+  <si>
+    <t>Discours court préparé et toujours le même permettant une communication claire et concise sur le changement en cours.</t>
+  </si>
+  <si>
+    <t>Analyse d'impacts</t>
+  </si>
+  <si>
+    <t>Placer les différents acteurs liés au projet dans une matrice (X = niveau d'impact, Y = niveau d'influence) et déterminer une stratégie pour chacun des cadrans.</t>
+  </si>
+  <si>
+    <t>comprendre, stratégie, analyse</t>
+  </si>
+  <si>
+    <t>Cartographie politique et stratégique des parties prenantes</t>
+  </si>
+  <si>
+    <t>Il s'agit de l'analyse des impacts pour les parties prenantes apportés par le projet de changement. Ne peut démarrer que quand le scope et besoins du projet sont relativement bien définis.</t>
+  </si>
+  <si>
+    <t>adhérer, comprendre, analyse</t>
+  </si>
+  <si>
+    <t>Analyse et gestion des préoccupations</t>
+  </si>
+  <si>
+    <t>modèle, comprendre, adhérer, analyse, stratégie</t>
+  </si>
+  <si>
+    <t>Analyse théorique basée sur une manière de voir la résistance au changement. Ce modèle se base sur les préoccupations et la gestion par la réponse de celles-ci à travers différents stades.</t>
+  </si>
+  <si>
+    <t>Définir une stratégie de participation</t>
+  </si>
+  <si>
+    <t>Cette stratégie se base sur 4 points à définir. Sur quoi les acteurs vont ils participer, la nature de cette participation, qui participera et le moment pour lancer cette participation.</t>
+  </si>
+  <si>
+    <t>stratégie, participer</t>
   </si>
 </sst>
 </file>
@@ -169,13 +286,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -236,8 +350,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{10F2806C-E9F6-4F68-B183-9F12382969E9}" name="Table1" displayName="Table1" ref="A1:D11" totalsRowShown="0" headerRowDxfId="5" dataDxfId="1">
-  <autoFilter ref="A1:D11" xr:uid="{10F2806C-E9F6-4F68-B183-9F12382969E9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{10F2806C-E9F6-4F68-B183-9F12382969E9}" name="Table1" displayName="Table1" ref="A1:D23" totalsRowShown="0" headerRowDxfId="5" dataDxfId="1">
+  <autoFilter ref="A1:D23" xr:uid="{10F2806C-E9F6-4F68-B183-9F12382969E9}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{2754BDFE-CC60-443C-9BAA-18CEABC07D01}" name="Outil" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{087C9761-2A1E-4247-AE26-DA46524F57CD}" name="Description" dataDxfId="3"/>
@@ -565,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F60179D4-D606-45E2-9272-BC7F4BB8B9F2}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.5546875" customWidth="1"/>
@@ -575,166 +689,325 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="3" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:4" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+      <c r="D8" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+      <c r="D10" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
+      <c r="D11" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>29</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/fichier_compl_toolbox.xlsx
+++ b/data/fichier_compl_toolbox.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vince\Desktop\GitHub\IT_CM_Toolbox_Website\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F75A5F-2ABB-4564-9F7C-4262742C2095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A55B9E19-A249-4E17-9078-1FB339F6E6D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CFE606A8-A71B-4F16-BD7A-880BC1F5037A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="72">
   <si>
     <t>Description</t>
   </si>
@@ -131,9 +131,6 @@
     <t>Manière de rencontrer et récolter de l'information sur un projet en mettant l'emphase sur la rencontre individuelle d'intervenants-clés et des questions spécifiques. Permet d'avoir des réponses précises sur des questions choisies au préalable.</t>
   </si>
   <si>
-    <t>définition projet, equipe</t>
-  </si>
-  <si>
     <t>Liste de questions pour aider à définir un projet de changement. Des questions sur la direction du projet, le pourquoi, la question du timing, les bénéfices et finalement comment s'y prendre.</t>
   </si>
   <si>
@@ -243,6 +240,18 @@
   </si>
   <si>
     <t>stratégie, participer</t>
+  </si>
+  <si>
+    <t>Créer un réseau d'agents du changement</t>
+  </si>
+  <si>
+    <t>Cette sratégie consiste à utiliser l'intérêt des acteurs pro changement comme moteur de révolution pour aider les autres acteurs à mieux appréhender le changement à venir. Ceux-ci vont être des acteurs clés qui feront office de relais entre les gestionnaires du changements et les acteurs affectés par ce changement.</t>
+  </si>
+  <si>
+    <t>définition projet, équipe</t>
+  </si>
+  <si>
+    <t>stratégie, participer, équipe</t>
   </si>
 </sst>
 </file>
@@ -350,8 +359,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{10F2806C-E9F6-4F68-B183-9F12382969E9}" name="Table1" displayName="Table1" ref="A1:D23" totalsRowShown="0" headerRowDxfId="5" dataDxfId="1">
-  <autoFilter ref="A1:D23" xr:uid="{10F2806C-E9F6-4F68-B183-9F12382969E9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{10F2806C-E9F6-4F68-B183-9F12382969E9}" name="Table1" displayName="Table1" ref="A1:D24" totalsRowShown="0" headerRowDxfId="5" dataDxfId="1">
+  <autoFilter ref="A1:D24" xr:uid="{10F2806C-E9F6-4F68-B183-9F12382969E9}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{2754BDFE-CC60-443C-9BAA-18CEABC07D01}" name="Outil" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{087C9761-2A1E-4247-AE26-DA46524F57CD}" name="Description" dataDxfId="3"/>
@@ -679,7 +688,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F60179D4-D606-45E2-9272-BC7F4BB8B9F2}">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.5546875" customWidth="1"/>
@@ -734,10 +743,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>29</v>
@@ -748,10 +757,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>29</v>
@@ -843,13 +852,13 @@
     </row>
     <row r="12" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>29</v>
@@ -857,13 +866,13 @@
     </row>
     <row r="13" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>29</v>
@@ -871,13 +880,13 @@
     </row>
     <row r="14" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>29</v>
@@ -885,13 +894,13 @@
     </row>
     <row r="15" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>29</v>
@@ -899,13 +908,13 @@
     </row>
     <row r="16" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>29</v>
@@ -913,13 +922,13 @@
     </row>
     <row r="17" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>29</v>
@@ -927,13 +936,13 @@
     </row>
     <row r="18" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>29</v>
@@ -941,13 +950,13 @@
     </row>
     <row r="19" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="C19" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>29</v>
@@ -955,13 +964,13 @@
     </row>
     <row r="20" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>29</v>
@@ -969,13 +978,13 @@
     </row>
     <row r="21" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>29</v>
@@ -983,13 +992,13 @@
     </row>
     <row r="22" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>29</v>
@@ -997,15 +1006,29 @@
     </row>
     <row r="23" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="B24" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>29</v>
       </c>
     </row>

--- a/data/fichier_compl_toolbox.xlsx
+++ b/data/fichier_compl_toolbox.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vince\Desktop\GitHub\IT_CM_Toolbox_Website\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A55B9E19-A249-4E17-9078-1FB339F6E6D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82944F74-7F30-4B30-B96C-CD26F7274BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CFE606A8-A71B-4F16-BD7A-880BC1F5037A}"/>
   </bookViews>
@@ -227,9 +227,6 @@
     <t>Analyse et gestion des préoccupations</t>
   </si>
   <si>
-    <t>modèle, comprendre, adhérer, analyse, stratégie</t>
-  </si>
-  <si>
     <t>Analyse théorique basée sur une manière de voir la résistance au changement. Ce modèle se base sur les préoccupations et la gestion par la réponse de celles-ci à travers différents stades.</t>
   </si>
   <si>
@@ -252,6 +249,9 @@
   </si>
   <si>
     <t>stratégie, participer, équipe</t>
+  </si>
+  <si>
+    <t>modèle, comprendre, adhérer, participer, analyse, stratégie</t>
   </si>
 </sst>
 </file>
@@ -746,7 +746,7 @@
         <v>32</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>29</v>
@@ -990,15 +990,15 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>62</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>29</v>
@@ -1006,13 +1006,13 @@
     </row>
     <row r="23" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>29</v>
@@ -1020,13 +1020,13 @@
     </row>
     <row r="24" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="C24" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>29</v>

--- a/data/fichier_compl_toolbox.xlsx
+++ b/data/fichier_compl_toolbox.xlsx
@@ -359,12 +359,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{10F2806C-E9F6-4F68-B183-9F12382969E9}" name="Table1" displayName="Table1" ref="A1:D24" totalsRowShown="0" headerRowDxfId="5" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{10F2806C-E9F6-4F68-B183-9F12382969E9}" name="Table1" displayName="Table1" ref="A1:D24" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
   <autoFilter ref="A1:D24" xr:uid="{10F2806C-E9F6-4F68-B183-9F12382969E9}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{2754BDFE-CC60-443C-9BAA-18CEABC07D01}" name="Outil" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{087C9761-2A1E-4247-AE26-DA46524F57CD}" name="Description" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{8B13619F-7B8E-4066-8EC4-55C4833E31BB}" name="Etiquettes" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{2754BDFE-CC60-443C-9BAA-18CEABC07D01}" name="Outil" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{087C9761-2A1E-4247-AE26-DA46524F57CD}" name="Description" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{8B13619F-7B8E-4066-8EC4-55C4833E31BB}" name="Etiquettes" dataDxfId="1"/>
     <tableColumn id="4" xr3:uid="{BACFC472-94B6-4AFD-B1F1-B1F90C606004}" name="Fini" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
